--- a/Docs/SimulacioVenda.xlsx
+++ b/Docs/SimulacioVenda.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319D7ECF-CE53-472E-9801-345361E69E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF696B6-F7BB-496A-A323-2795278C7851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F0182BAC-906E-4536-B8C7-199A601D9A89}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mov 15" sheetId="4" r:id="rId1"/>
-    <sheet name="Deusche" sheetId="1" r:id="rId2"/>
-    <sheet name="Taules" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="Mov 15" sheetId="4" r:id="rId2"/>
+    <sheet name="Deusche" sheetId="1" r:id="rId3"/>
+    <sheet name="Taules" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="38">
   <si>
     <t>Data Compra Orig</t>
   </si>
@@ -130,6 +131,24 @@
   </si>
   <si>
     <t>V5</t>
+  </si>
+  <si>
+    <t>Participacions a repartir:</t>
+  </si>
+  <si>
+    <t>Id:</t>
+  </si>
+  <si>
+    <t>Parts Util:</t>
+  </si>
+  <si>
+    <t>IdOrig:</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Correcte</t>
   </si>
 </sst>
 </file>
@@ -555,6 +574,397 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E2E389-BD5C-425A-AD33-D51EC9058A04}">
+  <dimension ref="B1:G32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="18.54296875" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" customWidth="1"/>
+    <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1">
+        <v>105.53</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>197</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>24.54</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3">
+        <v>24.54</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>203</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4">
+        <v>34.723999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>29.760999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>4.9630000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>205</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>46.265999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>46.265999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>197</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12">
+        <v>24.54</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>24.54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <v>203</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>34.723999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>29.760999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>4.9630000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>205</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17">
+        <v>0.73599999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18">
+        <v>0.73599999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21">
+        <v>24.54</v>
+      </c>
+      <c r="G21">
+        <f>+F21-F28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22">
+        <v>46.265999999999998</v>
+      </c>
+      <c r="G22">
+        <f>+F22-F29</f>
+        <v>45.53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23">
+        <v>29.760999999999999</v>
+      </c>
+      <c r="G23">
+        <f>+F23-F30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="G24">
+        <f>+F24-F31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F25" s="1">
+        <f>SUM(F21:F24)</f>
+        <v>105.52999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28">
+        <v>24.54</v>
+      </c>
+      <c r="G28">
+        <f>F21</f>
+        <v>24.54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29">
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="G29">
+        <v>35.46</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30">
+        <v>29.760999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31">
+        <v>4.9630000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F32" s="1">
+        <f>SUM(F28:F31)</f>
+        <v>60</v>
+      </c>
+      <c r="G32">
+        <f>60-SUM(G28:G31)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCF58976-EAE7-4A0A-A776-E4303DC2CBF0}">
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1188,7 +1598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8360068-02BA-4318-81EB-89A66DB152B1}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1536,7 +1946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2FD33C-E4FE-42DC-98BD-EE611A662A9A}">
   <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Docs/SimulacioVenda.xlsx
+++ b/Docs/SimulacioVenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF696B6-F7BB-496A-A323-2795278C7851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E9E6A-15FB-41A0-84A8-091921BBC317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F0182BAC-906E-4536-B8C7-199A601D9A89}"/>
   </bookViews>
@@ -215,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -261,6 +261,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,16 +576,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E2E389-BD5C-425A-AD33-D51EC9058A04}">
-  <dimension ref="B1:G32"/>
+  <dimension ref="B1:I32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.54296875" customWidth="1"/>
     <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.08984375" customWidth="1"/>
     <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>32</v>
       </c>
@@ -592,7 +594,7 @@
         <v>105.53</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>33</v>
       </c>
@@ -606,7 +608,7 @@
         <v>24.54</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>35</v>
       </c>
@@ -620,7 +622,7 @@
         <v>24.54</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>33</v>
       </c>
@@ -634,7 +636,7 @@
         <v>34.723999999999997</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>35</v>
       </c>
@@ -647,8 +649,11 @@
       <c r="F5">
         <v>29.760999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="I5" s="27">
+        <v>16861.349999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>35</v>
       </c>
@@ -661,8 +666,11 @@
       <c r="F6">
         <v>4.9630000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="I6" s="26">
+        <v>4185.07</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>33</v>
       </c>
@@ -675,8 +683,11 @@
       <c r="E7">
         <v>46.265999999999998</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="I7" s="27">
+        <v>68458.62</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>35</v>
       </c>
@@ -689,8 +700,12 @@
       <c r="F8">
         <v>46.265999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="I8" s="26">
+        <f>SUM(I5:I7)</f>
+        <v>89505.04</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>32</v>
       </c>
@@ -698,7 +713,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>33</v>
       </c>
@@ -712,7 +727,7 @@
         <v>24.54</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>35</v>
       </c>
@@ -726,7 +741,7 @@
         <v>24.54</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>33</v>
       </c>
@@ -740,7 +755,7 @@
         <v>34.723999999999997</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>35</v>
       </c>
@@ -754,7 +769,7 @@
         <v>29.760999999999999</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
         <v>35</v>
       </c>

--- a/Docs/SimulacioVenda.xlsx
+++ b/Docs/SimulacioVenda.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E9E6A-15FB-41A0-84A8-091921BBC317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24028398-6CB1-4A3F-A7B7-F6B56602772F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F0182BAC-906E-4536-B8C7-199A601D9A89}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{F0182BAC-906E-4536-B8C7-199A601D9A89}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
-    <sheet name="Mov 15" sheetId="4" r:id="rId2"/>
-    <sheet name="Deusche" sheetId="1" r:id="rId3"/>
-    <sheet name="Taules" sheetId="2" r:id="rId4"/>
+    <sheet name="Mov 15" sheetId="4" r:id="rId1"/>
+    <sheet name="Deusche" sheetId="1" r:id="rId2"/>
+    <sheet name="Taules" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
   <si>
     <t>Data Compra Orig</t>
   </si>
@@ -131,24 +130,6 @@
   </si>
   <si>
     <t>V5</t>
-  </si>
-  <si>
-    <t>Participacions a repartir:</t>
-  </si>
-  <si>
-    <t>Id:</t>
-  </si>
-  <si>
-    <t>Parts Util:</t>
-  </si>
-  <si>
-    <t>IdOrig:</t>
-  </si>
-  <si>
-    <t>Actual</t>
-  </si>
-  <si>
-    <t>Correcte</t>
   </si>
 </sst>
 </file>
@@ -261,7 +242,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,402 +558,741 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E2E389-BD5C-425A-AD33-D51EC9058A04}">
-  <dimension ref="B1:I32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCF58976-EAE7-4A0A-A776-E4303DC2CBF0}">
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" customWidth="1"/>
-    <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1">
-        <v>105.53</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2">
-        <v>197</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2">
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="19">
+        <v>15</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="20">
+        <v>36841</v>
+      </c>
+      <c r="D3" s="19">
+        <v>679.64</v>
+      </c>
+      <c r="E3" s="21">
+        <v>22.992000000000001</v>
+      </c>
+      <c r="F3" s="21">
+        <v>15626.31</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3">
+        <f>D3</f>
+        <v>679.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="24">
+        <v>23</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="20">
+        <v>41383</v>
+      </c>
+      <c r="D4" s="19">
+        <v>679.64</v>
+      </c>
+      <c r="E4" s="21">
+        <v>8.1097999999999999</v>
+      </c>
+      <c r="F4" s="21">
+        <v>5511.77</v>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="26">
+        <f>IF(ISNUMBER(SEARCH("v",B4,1)),H3-D4,H3+D4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="19">
+        <v>16</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="20">
+        <v>41166</v>
+      </c>
+      <c r="D7" s="27">
+        <v>547.64509999999996</v>
+      </c>
+      <c r="E7" s="21">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="F7" s="21">
+        <v>10000</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7">
+        <f>D7</f>
+        <v>547.64509999999996</v>
+      </c>
+      <c r="I7">
+        <f>SUM(D7:D9)</f>
+        <v>1838.3261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>17</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="20">
+        <v>41377</v>
+      </c>
+      <c r="D8" s="27">
+        <v>1010.611</v>
+      </c>
+      <c r="E8" s="21">
+        <v>19.79</v>
+      </c>
+      <c r="F8" s="21">
+        <v>19999.990000000002</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="26">
+        <f t="shared" ref="H8:H10" si="0">IF(ISNUMBER(SEARCH("v",B8,1)),H7-D8,H7+D8)</f>
+        <v>1558.2561000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="24">
+        <v>24</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="20">
+        <v>41383</v>
+      </c>
+      <c r="D9" s="27">
+        <v>280.07</v>
+      </c>
+      <c r="E9" s="21">
+        <v>19.68</v>
+      </c>
+      <c r="F9" s="21">
+        <v>5511.77</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="26">
+        <f t="shared" si="0"/>
+        <v>1838.3261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>25</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="20">
+        <v>41439</v>
+      </c>
+      <c r="D10" s="27">
+        <v>1838.3261</v>
+      </c>
+      <c r="E10" s="21">
+        <v>18.95</v>
+      </c>
+      <c r="F10" s="21">
+        <v>34836.28</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="24">
+        <v>26</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="20">
+        <v>41439</v>
+      </c>
+      <c r="D13" s="27">
+        <v>249.34710000000001</v>
+      </c>
+      <c r="E13" s="21">
+        <v>139.71</v>
+      </c>
+      <c r="F13" s="21">
+        <v>34836.28</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13">
+        <f>D13</f>
+        <v>249.34710000000001</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="19">
+        <v>28</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="20">
+        <v>41794</v>
+      </c>
+      <c r="D14" s="27">
+        <v>249</v>
+      </c>
+      <c r="E14" s="21">
+        <v>172.04</v>
+      </c>
+      <c r="F14" s="21">
+        <v>42837.96</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="26">
+        <f t="shared" ref="H14:H16" si="1">IF(ISNUMBER(SEARCH("v",B14,1)),H13-D14,H13+D14)</f>
+        <v>0.34710000000001173</v>
+      </c>
+      <c r="J14" s="21">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="19">
+        <v>31</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="20">
+        <v>41976</v>
+      </c>
+      <c r="D15" s="27">
+        <v>264.18049999999999</v>
+      </c>
+      <c r="E15" s="21">
+        <v>168.57</v>
+      </c>
+      <c r="F15" s="21">
+        <v>44532.91</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" s="26">
+        <f t="shared" si="1"/>
+        <v>264.52760000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="19">
+        <v>91</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="20">
+        <v>42201</v>
+      </c>
+      <c r="D16" s="27">
+        <v>259.52999999999997</v>
+      </c>
+      <c r="E16" s="21">
+        <v>207.11</v>
+      </c>
+      <c r="F16" s="21">
+        <v>53751.26</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="26">
+        <f t="shared" si="1"/>
+        <v>4.997600000000034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <v>27</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="20">
+        <v>41521</v>
+      </c>
+      <c r="D19" s="23">
+        <v>58.502000000000002</v>
+      </c>
+      <c r="E19" s="21">
+        <v>17.093299999999999</v>
+      </c>
+      <c r="F19" s="21">
+        <v>999.99</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19">
+        <f>D19</f>
+        <v>58.502000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="24">
+        <v>29</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="20">
+        <v>41794</v>
+      </c>
+      <c r="D20" s="23">
+        <v>2347.326</v>
+      </c>
+      <c r="E20" s="21">
+        <v>18.249700000000001</v>
+      </c>
+      <c r="F20" s="21">
+        <v>42837.96</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="26">
+        <f t="shared" ref="H20:H24" si="2">IF(ISNUMBER(SEARCH("v",B20,1)),H19-D20,H19+D20)</f>
+        <v>2405.828</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="19">
+        <v>30</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="20">
+        <v>41971</v>
+      </c>
+      <c r="D21" s="23">
+        <v>2404</v>
+      </c>
+      <c r="E21" s="21">
+        <v>18.5245</v>
+      </c>
+      <c r="F21" s="21">
+        <v>44532.91</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="26">
+        <f t="shared" si="2"/>
+        <v>1.8279999999999745</v>
+      </c>
+      <c r="J21">
+        <v>27</v>
+      </c>
+      <c r="K21">
+        <v>15</v>
+      </c>
+      <c r="L21">
+        <v>16</v>
+      </c>
+      <c r="M21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="24">
+        <v>92</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="20">
+        <v>42202</v>
+      </c>
+      <c r="D22" s="23">
+        <v>2922.36</v>
+      </c>
+      <c r="E22" s="21">
+        <v>18.3931</v>
+      </c>
+      <c r="F22" s="21">
+        <v>53751.26</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="26">
+        <f t="shared" si="2"/>
+        <v>2924.1880000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="19">
+        <v>100</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="20">
+        <v>42279</v>
+      </c>
+      <c r="D23" s="23">
+        <v>2879.2429999999999</v>
+      </c>
+      <c r="E23" s="21">
+        <v>18.063199999999998</v>
+      </c>
+      <c r="F23" s="21">
+        <v>52008.35</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="26">
+        <f t="shared" si="2"/>
+        <v>44.945000000000164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="19">
+        <v>170</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="20">
+        <v>43516</v>
+      </c>
+      <c r="D24" s="23">
+        <v>44.945</v>
+      </c>
+      <c r="E24" s="21">
+        <v>19.726199999999999</v>
+      </c>
+      <c r="F24" s="21">
+        <v>886.59</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="26">
+        <f t="shared" si="2"/>
+        <v>1.6342482922482304E-13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" s="19">
+        <v>101</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="20">
+        <v>42279</v>
+      </c>
+      <c r="D27" s="23">
+        <v>160.75280000000001</v>
+      </c>
+      <c r="E27" s="21">
+        <v>323.52999999999997</v>
+      </c>
+      <c r="F27" s="21">
+        <v>52008.35</v>
+      </c>
+      <c r="G27" s="21"/>
+      <c r="H27">
+        <f>D27</f>
+        <v>160.75280000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="19">
+        <v>172</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="20">
+        <v>43525</v>
+      </c>
+      <c r="D28" s="23">
+        <v>80.752799999999993</v>
+      </c>
+      <c r="E28" s="21">
+        <v>375.55</v>
+      </c>
+      <c r="F28" s="21">
+        <v>30326.71</v>
+      </c>
+      <c r="G28" s="21"/>
+      <c r="H28" s="26">
+        <f t="shared" ref="H28:H30" si="3">IF(ISNUMBER(SEARCH("v",B28,1)),H27-D28,H27+D28)</f>
+        <v>80.000000000000014</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
+        <v>196</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="20">
+        <v>44469</v>
+      </c>
+      <c r="D29" s="23">
+        <v>20</v>
+      </c>
+      <c r="E29" s="21">
+        <v>533.87</v>
+      </c>
+      <c r="F29" s="21">
+        <v>10677.4</v>
+      </c>
+      <c r="G29" s="21"/>
+      <c r="H29" s="26">
+        <f t="shared" si="3"/>
+        <v>60.000000000000014</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="19">
+        <v>204</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="20">
+        <v>44522</v>
+      </c>
+      <c r="D30" s="23">
         <v>35</v>
       </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3">
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4">
-        <v>203</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4">
-        <v>34.723999999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
-        <v>29.760999999999999</v>
-      </c>
-      <c r="I5" s="27">
-        <v>16861.349999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6">
-        <v>4.9630000000000001</v>
-      </c>
-      <c r="I6" s="26">
-        <v>4185.07</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>205</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>46.265999999999998</v>
-      </c>
-      <c r="I7" s="27">
-        <v>68458.62</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8">
-        <v>46.265999999999998</v>
-      </c>
-      <c r="I8" s="26">
-        <f>SUM(I5:I7)</f>
-        <v>89505.04</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>197</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12">
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13">
-        <v>17</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13">
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14">
-        <v>203</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14">
-        <v>34.723999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15">
-        <v>7</v>
-      </c>
-      <c r="E15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15">
-        <v>29.760999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16">
-        <v>37</v>
-      </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16">
-        <v>4.9630000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17">
-        <v>205</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17">
-        <v>0.73599999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18">
-        <v>17</v>
-      </c>
-      <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18">
-        <v>0.73599999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21">
-        <v>17</v>
-      </c>
-      <c r="E21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21">
-        <v>24.54</v>
-      </c>
-      <c r="G21">
-        <f>+F21-F28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22">
-        <v>17</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22">
-        <v>46.265999999999998</v>
-      </c>
-      <c r="G22">
-        <f>+F22-F29</f>
-        <v>45.53</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23">
-        <v>29.760999999999999</v>
-      </c>
-      <c r="G23">
-        <f>+F23-F30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C24" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24">
-        <v>37</v>
-      </c>
-      <c r="E24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24">
-        <v>4.9630000000000001</v>
-      </c>
-      <c r="G24">
-        <f>+F24-F31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="F25" s="1">
-        <f>SUM(F21:F24)</f>
-        <v>105.52999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="F27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28">
-        <v>17</v>
-      </c>
-      <c r="E28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28">
-        <v>24.54</v>
-      </c>
-      <c r="G28">
-        <f>F21</f>
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C29" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29">
-        <v>17</v>
-      </c>
-      <c r="E29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29">
-        <v>0.73599999999999999</v>
-      </c>
-      <c r="G29">
-        <v>35.46</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30">
-        <v>29.760999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31">
-        <v>37</v>
-      </c>
-      <c r="E31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31">
-        <v>4.9630000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="F32" s="1">
-        <f>SUM(F28:F31)</f>
-        <v>60</v>
-      </c>
-      <c r="G32">
-        <f>60-SUM(G28:G31)</f>
-        <v>0</v>
+      <c r="E30" s="21">
+        <v>574.70000000000005</v>
+      </c>
+      <c r="F30" s="21">
+        <v>20114.5</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="26">
+        <f t="shared" si="3"/>
+        <v>25.000000000000014</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="19">
+        <v>1</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="20">
+        <v>41172</v>
+      </c>
+      <c r="D33" s="23">
+        <v>325.52199999999999</v>
+      </c>
+      <c r="E33" s="21">
+        <v>30.719899999999999</v>
+      </c>
+      <c r="F33" s="21">
+        <v>9999.99</v>
+      </c>
+      <c r="G33" s="21"/>
+      <c r="H33">
+        <f>D33</f>
+        <v>325.52199999999999</v>
+      </c>
+      <c r="I33">
+        <f>D33</f>
+        <v>325.52199999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="19">
+        <v>2</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="20">
+        <v>41187</v>
+      </c>
+      <c r="D34" s="23">
+        <v>1267.6880000000001</v>
+      </c>
+      <c r="E34" s="21">
+        <v>31.5535</v>
+      </c>
+      <c r="F34" s="21">
+        <v>39999.980000000003</v>
+      </c>
+      <c r="G34" s="21"/>
+      <c r="H34" s="26">
+        <f t="shared" ref="H34:H37" si="4">IF(ISNUMBER(SEARCH("v",B34,1)),H33-D34,H33+D34)</f>
+        <v>1593.21</v>
+      </c>
+      <c r="I34" s="26">
+        <f>D36-I33</f>
+        <v>1090.0600000000002</v>
+      </c>
+      <c r="J34" s="26">
+        <f>D34-I34</f>
+        <v>177.62799999999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="19">
+        <v>3</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="20">
+        <v>41410</v>
+      </c>
+      <c r="D35" s="23">
+        <v>522.37400000000002</v>
+      </c>
+      <c r="E35" s="21">
+        <v>38.286799999999999</v>
+      </c>
+      <c r="F35" s="21">
+        <v>20000.02</v>
+      </c>
+      <c r="G35" s="21"/>
+      <c r="H35" s="26">
+        <f t="shared" si="4"/>
+        <v>2115.5839999999998</v>
+      </c>
+      <c r="J35" s="26">
+        <f>D37-J34</f>
+        <v>0.37200000000007094</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="19">
+        <v>4</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="20">
+        <v>41438</v>
+      </c>
+      <c r="D36" s="23">
+        <v>1415.5820000000001</v>
+      </c>
+      <c r="E36" s="21">
+        <v>33.983400000000003</v>
+      </c>
+      <c r="F36" s="21">
+        <v>48106.28</v>
+      </c>
+      <c r="G36" s="21"/>
+      <c r="H36" s="26">
+        <f t="shared" si="4"/>
+        <v>700.00199999999973</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="19">
+        <v>5</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="20">
+        <v>41492</v>
+      </c>
+      <c r="D37" s="23">
+        <v>178</v>
+      </c>
+      <c r="E37" s="21">
+        <v>33.8964</v>
+      </c>
+      <c r="F37" s="21">
+        <v>6033.56</v>
+      </c>
+      <c r="G37" s="21"/>
+      <c r="H37" s="26">
+        <f t="shared" si="4"/>
+        <v>522.00199999999973</v>
       </c>
     </row>
   </sheetData>
@@ -980,640 +1302,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCF58976-EAE7-4A0A-A776-E4303DC2CBF0}">
-  <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="19">
-        <v>15</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="20">
-        <v>36841</v>
-      </c>
-      <c r="D3" s="19">
-        <v>679.64</v>
-      </c>
-      <c r="E3" s="21">
-        <v>22.992000000000001</v>
-      </c>
-      <c r="F3" s="21">
-        <v>15626.31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="24">
-        <v>23</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="20">
-        <v>41383</v>
-      </c>
-      <c r="D4" s="19">
-        <v>679.64</v>
-      </c>
-      <c r="E4" s="21">
-        <v>8.1097999999999999</v>
-      </c>
-      <c r="F4" s="21">
-        <v>5511.77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="19">
-        <v>16</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="20">
-        <v>41166</v>
-      </c>
-      <c r="D7" s="19">
-        <v>547.64509999999996</v>
-      </c>
-      <c r="E7" s="21">
-        <v>18.260000000000002</v>
-      </c>
-      <c r="F7" s="21">
-        <v>10000</v>
-      </c>
-      <c r="H7">
-        <f>SUM(D7:D9)</f>
-        <v>1838.3261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="19">
-        <v>17</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="20">
-        <v>41377</v>
-      </c>
-      <c r="D8" s="23">
-        <v>1010.611</v>
-      </c>
-      <c r="E8" s="21">
-        <v>19.79</v>
-      </c>
-      <c r="F8" s="21">
-        <v>19999.990000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="24">
-        <v>24</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="20">
-        <v>41383</v>
-      </c>
-      <c r="D9" s="19">
-        <v>280.07</v>
-      </c>
-      <c r="E9" s="21">
-        <v>19.68</v>
-      </c>
-      <c r="F9" s="21">
-        <v>5511.77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="19">
-        <v>25</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="20">
-        <v>41439</v>
-      </c>
-      <c r="D10" s="23">
-        <v>1838.3261</v>
-      </c>
-      <c r="E10" s="21">
-        <v>18.95</v>
-      </c>
-      <c r="F10" s="21">
-        <v>34836.28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="24">
-        <v>26</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="20">
-        <v>41439</v>
-      </c>
-      <c r="D13" s="19">
-        <v>249.34710000000001</v>
-      </c>
-      <c r="E13" s="21">
-        <v>139.71</v>
-      </c>
-      <c r="F13" s="21">
-        <v>34836.28</v>
-      </c>
-      <c r="G13" s="21"/>
-      <c r="I13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="19">
-        <v>28</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="20">
-        <v>41794</v>
-      </c>
-      <c r="D14" s="19">
-        <v>249</v>
-      </c>
-      <c r="E14" s="21">
-        <v>172.04</v>
-      </c>
-      <c r="F14" s="21">
-        <v>42837.96</v>
-      </c>
-      <c r="G14" s="21">
-        <f>D14</f>
-        <v>249</v>
-      </c>
-      <c r="I14" s="21">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="19">
-        <v>31</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="20">
-        <v>41976</v>
-      </c>
-      <c r="D15" s="19">
-        <v>264.18049999999999</v>
-      </c>
-      <c r="E15" s="21">
-        <v>168.57</v>
-      </c>
-      <c r="F15" s="21">
-        <v>44532.91</v>
-      </c>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="19">
-        <v>91</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="20">
-        <v>42201</v>
-      </c>
-      <c r="D16" s="19">
-        <v>259.52999999999997</v>
-      </c>
-      <c r="E16" s="21">
-        <v>207.11</v>
-      </c>
-      <c r="F16" s="21">
-        <v>53751.26</v>
-      </c>
-      <c r="G16" s="21">
-        <f>D13-D14</f>
-        <v>0.34710000000001173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="19">
-        <v>27</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="20">
-        <v>41521</v>
-      </c>
-      <c r="D19" s="19">
-        <v>58.502000000000002</v>
-      </c>
-      <c r="E19" s="21">
-        <v>17.093299999999999</v>
-      </c>
-      <c r="F19" s="21">
-        <v>999.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="24">
-        <v>29</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="20">
-        <v>41794</v>
-      </c>
-      <c r="D20" s="23">
-        <v>2347.326</v>
-      </c>
-      <c r="E20" s="21">
-        <v>18.249700000000001</v>
-      </c>
-      <c r="F20" s="21">
-        <v>42837.96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="19">
-        <v>30</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="20">
-        <v>41971</v>
-      </c>
-      <c r="D21" s="23">
-        <v>2404</v>
-      </c>
-      <c r="E21" s="21">
-        <v>18.5245</v>
-      </c>
-      <c r="F21" s="21">
-        <v>44532.91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="24">
-        <v>92</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="20">
-        <v>42202</v>
-      </c>
-      <c r="D22" s="23">
-        <v>2922.36</v>
-      </c>
-      <c r="E22" s="21">
-        <v>18.3931</v>
-      </c>
-      <c r="F22" s="21">
-        <v>53751.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="19">
-        <v>100</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="20">
-        <v>42279</v>
-      </c>
-      <c r="D23" s="23">
-        <v>2879.2429999999999</v>
-      </c>
-      <c r="E23" s="21">
-        <v>18.063199999999998</v>
-      </c>
-      <c r="F23" s="21">
-        <v>52008.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="19">
-        <v>170</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="20">
-        <v>43516</v>
-      </c>
-      <c r="D24" s="19">
-        <v>44.945</v>
-      </c>
-      <c r="E24" s="21">
-        <v>19.726199999999999</v>
-      </c>
-      <c r="F24" s="21">
-        <v>886.59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="19">
-        <v>101</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="20">
-        <v>42279</v>
-      </c>
-      <c r="D27" s="19">
-        <v>160.75280000000001</v>
-      </c>
-      <c r="E27" s="21">
-        <v>323.52999999999997</v>
-      </c>
-      <c r="F27" s="21">
-        <v>52008.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="19">
-        <v>172</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="20">
-        <v>43525</v>
-      </c>
-      <c r="D28" s="19">
-        <v>80.752799999999993</v>
-      </c>
-      <c r="E28" s="21">
-        <v>375.55</v>
-      </c>
-      <c r="F28" s="21">
-        <v>30326.71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="19">
-        <v>196</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="20">
-        <v>44469</v>
-      </c>
-      <c r="D29" s="19">
-        <v>20</v>
-      </c>
-      <c r="E29" s="21">
-        <v>533.87</v>
-      </c>
-      <c r="F29" s="21">
-        <v>10677.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="19">
-        <v>204</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="20">
-        <v>44522</v>
-      </c>
-      <c r="D30" s="19">
-        <v>35</v>
-      </c>
-      <c r="E30" s="21">
-        <v>574.70000000000005</v>
-      </c>
-      <c r="F30" s="21">
-        <v>20114.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="19">
-        <v>1</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="20">
-        <v>41172</v>
-      </c>
-      <c r="D33" s="19">
-        <v>325.52199999999999</v>
-      </c>
-      <c r="E33" s="21">
-        <v>30.719899999999999</v>
-      </c>
-      <c r="F33" s="21">
-        <v>9999.99</v>
-      </c>
-      <c r="G33">
-        <f>D33</f>
-        <v>325.52199999999999</v>
-      </c>
-      <c r="H33">
-        <f>D33</f>
-        <v>325.52199999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="19">
-        <v>2</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="20">
-        <v>41187</v>
-      </c>
-      <c r="D34" s="23">
-        <v>1267.6880000000001</v>
-      </c>
-      <c r="E34" s="21">
-        <v>31.5535</v>
-      </c>
-      <c r="F34" s="21">
-        <v>39999.980000000003</v>
-      </c>
-      <c r="G34" s="26">
-        <f>G33+D34</f>
-        <v>1593.21</v>
-      </c>
-      <c r="H34" s="26">
-        <f>D36-H33</f>
-        <v>1090.0600000000002</v>
-      </c>
-      <c r="I34" s="26">
-        <f>D34-H34</f>
-        <v>177.62799999999993</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="19">
-        <v>3</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="20">
-        <v>41410</v>
-      </c>
-      <c r="D35" s="19">
-        <v>522.37400000000002</v>
-      </c>
-      <c r="E35" s="21">
-        <v>38.286799999999999</v>
-      </c>
-      <c r="F35" s="21">
-        <v>20000.02</v>
-      </c>
-      <c r="G35" s="26">
-        <f>G34+D35</f>
-        <v>2115.5839999999998</v>
-      </c>
-      <c r="I35" s="26">
-        <f>D37-I34</f>
-        <v>0.37200000000007094</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="19">
-        <v>4</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="20">
-        <v>41438</v>
-      </c>
-      <c r="D36" s="23">
-        <v>1415.5820000000001</v>
-      </c>
-      <c r="E36" s="21">
-        <v>33.983400000000003</v>
-      </c>
-      <c r="F36" s="21">
-        <v>48106.28</v>
-      </c>
-      <c r="G36" s="26">
-        <f>G35-D36</f>
-        <v>700.00199999999973</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="19">
-        <v>5</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="20">
-        <v>41492</v>
-      </c>
-      <c r="D37" s="19">
-        <v>178</v>
-      </c>
-      <c r="E37" s="21">
-        <v>33.8964</v>
-      </c>
-      <c r="F37" s="21">
-        <v>6033.56</v>
-      </c>
-      <c r="G37" s="26">
-        <f>G36-D37</f>
-        <v>522.00199999999973</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8360068-02BA-4318-81EB-89A66DB152B1}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1961,7 +1649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2FD33C-E4FE-42DC-98BD-EE611A662A9A}">
   <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
